--- a/stufe-5/dok/migrate-ig-to-ig-publisher-ptdata-1969/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/dok/migrate-ig-to-ig-publisher-ptdata-1969/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-09T15:29:45+00:00</t>
+    <t>2025-12-10T09:33:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
